--- a/staff.xlsx
+++ b/staff.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\itdep\OneDrive\Documents\Qian\ENameCard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A94B34E9-3825-453C-BD66-5B4019A4B5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC5FFC8-0A3A-4231-AC79-75AFD0ACAE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="staff" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t>id</t>
   </si>
@@ -90,9 +90,6 @@
     <t>CFO</t>
   </si>
   <si>
-    <t>iuhiuhnaiqoaij@gmailcom</t>
-  </si>
-  <si>
     <t>images/jared.png</t>
   </si>
   <si>
@@ -109,6 +106,12 @@
   </si>
   <si>
     <t>images/kelly.png</t>
+  </si>
+  <si>
+    <t>iuhiuhnaiqoaij@gmail.com</t>
+  </si>
+  <si>
+    <t>https://www.sengli.com.my/mobile/home</t>
   </si>
 </sst>
 </file>
@@ -656,6 +659,7 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="5" max="5" width="12.88671875"/>
+    <col min="6" max="6" width="54.21875" customWidth="1"/>
     <col min="7" max="7" width="12.88671875"/>
   </cols>
   <sheetData>
@@ -710,6 +714,9 @@
       <c r="G2">
         <v>60143986456</v>
       </c>
+      <c r="H2" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="I2" t="s">
         <v>14</v>
       </c>
@@ -731,24 +738,27 @@
         <v>60167358581</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G3">
         <v>60167358581</v>
       </c>
+      <c r="H3" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
         <v>20</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
@@ -757,13 +767,16 @@
         <v>60167278456</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G4">
         <v>60167278456</v>
       </c>
+      <c r="H4" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="I4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -771,6 +784,9 @@
     <hyperlink ref="F2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="F3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="F4" r:id="rId3" xr:uid="{B33D1EDA-7882-450B-9ABE-040E4146DE2F}"/>
+    <hyperlink ref="H2" r:id="rId4" xr:uid="{686028C9-B72C-4774-A89F-6CAEAF82BEFB}"/>
+    <hyperlink ref="H3" r:id="rId5" xr:uid="{47AE87C6-D529-49D2-BF74-8F7058E0490C}"/>
+    <hyperlink ref="H4" r:id="rId6" xr:uid="{08F658A4-B729-4131-8B3A-F1D737844990}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/staff.xlsx
+++ b/staff.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\itdep\OneDrive\Documents\Qian\ENameCard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC5FFC8-0A3A-4231-AC79-75AFD0ACAE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A3464C-7F44-4A98-BABE-1FAE66986FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="staff" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
   <si>
     <t>id</t>
   </si>
@@ -72,12 +72,15 @@
     <t>Data</t>
   </si>
   <si>
-    <t>SL</t>
+    <t>SENG LI MARKETING SDN BHD</t>
   </si>
   <si>
     <t>qianhuistudyarea@gmail.com</t>
   </si>
   <si>
+    <t>https://www.sengli.com.my/mobile/home</t>
+  </si>
+  <si>
     <t>images/qianhui.png</t>
   </si>
   <si>
@@ -99,19 +102,31 @@
     <t>Kelly Chan</t>
   </si>
   <si>
-    <t>AP</t>
-  </si>
-  <si>
-    <t>annielss62@gmail.com</t>
-  </si>
-  <si>
     <t>images/kelly.png</t>
   </si>
   <si>
-    <t>iuhiuhnaiqoaij@gmail.com</t>
-  </si>
-  <si>
-    <t>https://www.sengli.com.my/mobile/home</t>
+    <t>Account (AP)</t>
+  </si>
+  <si>
+    <t>Admin Manager</t>
+  </si>
+  <si>
+    <t>Lee Man Man</t>
+  </si>
+  <si>
+    <t>info@sengli.com.my</t>
+  </si>
+  <si>
+    <t xml:space="preserve">man858100@gmail </t>
+  </si>
+  <si>
+    <t>images/man.png</t>
+  </si>
+  <si>
+    <t>man</t>
+  </si>
+  <si>
+    <t>jaredlow@sengli.com.my</t>
   </si>
 </sst>
 </file>
@@ -131,6 +146,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -655,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="5" max="5" width="12.88671875"/>
@@ -715,78 +731,109 @@
         <v>60143986456</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3">
-        <v>60167358581</v>
+        <v>60107608581</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>60167358581</v>
+        <v>60107608581</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="I3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4">
-        <v>60167278456</v>
+        <v>60167388581</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4">
+        <v>60167388581</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" t="s">
         <v>22</v>
       </c>
-      <c r="G4">
-        <v>60167278456</v>
-      </c>
-      <c r="H4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
         <v>25</v>
       </c>
-      <c r="I4" t="s">
-        <v>23</v>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>60129228661</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5">
+        <v>60129228661</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="F3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="F4" r:id="rId3" xr:uid="{B33D1EDA-7882-450B-9ABE-040E4146DE2F}"/>
-    <hyperlink ref="H2" r:id="rId4" xr:uid="{686028C9-B72C-4774-A89F-6CAEAF82BEFB}"/>
-    <hyperlink ref="H3" r:id="rId5" xr:uid="{47AE87C6-D529-49D2-BF74-8F7058E0490C}"/>
-    <hyperlink ref="H4" r:id="rId6" xr:uid="{08F658A4-B729-4131-8B3A-F1D737844990}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="H2" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="H3" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="H4" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="F5" r:id="rId7" xr:uid="{589B0F6A-F69F-4657-B72B-EC48CA58772C}"/>
+    <hyperlink ref="H5" r:id="rId8" xr:uid="{80A79679-96C5-4F25-9652-5F47437AC14D}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/staff.xlsx
+++ b/staff.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\itdep\OneDrive\Documents\Qian\ENameCard\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A3464C-7F44-4A98-BABE-1FAE66986FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="23040" windowHeight="9708"/>
   </bookViews>
   <sheets>
     <sheet name="staff" sheetId="1" r:id="rId1"/>
@@ -24,10 +18,9 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -93,6 +86,9 @@
     <t>CFO</t>
   </si>
   <si>
+    <t>jaredlow@sengli.com.my</t>
+  </si>
+  <si>
     <t>images/jared.png</t>
   </si>
   <si>
@@ -102,38 +98,41 @@
     <t>Kelly Chan</t>
   </si>
   <si>
+    <t>Account (AP)</t>
+  </si>
+  <si>
+    <t>info@sengli.com.my</t>
+  </si>
+  <si>
     <t>images/kelly.png</t>
   </si>
   <si>
-    <t>Account (AP)</t>
+    <t>man</t>
+  </si>
+  <si>
+    <t>Lee Man Man</t>
   </si>
   <si>
     <t>Admin Manager</t>
   </si>
   <si>
-    <t>Lee Man Man</t>
-  </si>
-  <si>
-    <t>info@sengli.com.my</t>
-  </si>
-  <si>
-    <t xml:space="preserve">man858100@gmail </t>
+    <t>man858100@gmail.com</t>
   </si>
   <si>
     <t>images/man.png</t>
-  </si>
-  <si>
-    <t>man</t>
-  </si>
-  <si>
-    <t>jaredlow@sengli.com.my</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,16 +148,338 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -166,12 +487,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -179,163 +739,93 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
+        <b val="1"/>
         <color theme="1"/>
       </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -346,7 +836,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -374,40 +864,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -665,18 +1269,18 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelRow="4"/>
   <cols>
-    <col min="5" max="5" width="12.88671875"/>
-    <col min="6" max="6" width="54.21875" customWidth="1"/>
-    <col min="7" max="7" width="12.88671875"/>
+    <col min="5" max="5" width="12.8888888888889"/>
+    <col min="6" max="6" width="54.2222222222222" customWidth="1"/>
+    <col min="7" max="7" width="12.8888888888889"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -754,7 +1358,7 @@
         <v>60107608581</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G3">
         <v>60107608581</v>
@@ -763,15 +1367,15 @@
         <v>14</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
         <v>23</v>
@@ -783,7 +1387,7 @@
         <v>60167388581</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G4">
         <v>60167388581</v>
@@ -792,18 +1396,18 @@
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
@@ -812,7 +1416,7 @@
         <v>60129228661</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G5">
         <v>60129228661</v>
@@ -821,20 +1425,21 @@
         <v>14</v>
       </c>
       <c r="I5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="F3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="F4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="H2" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="H3" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="H4" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="F5" r:id="rId7" xr:uid="{589B0F6A-F69F-4657-B72B-EC48CA58772C}"/>
-    <hyperlink ref="H5" r:id="rId8" xr:uid="{80A79679-96C5-4F25-9652-5F47437AC14D}"/>
+    <hyperlink ref="F2" r:id="rId1" display="qianhuistudyarea@gmail.com"/>
+    <hyperlink ref="F3" r:id="rId2" display="jaredlow@sengli.com.my"/>
+    <hyperlink ref="F4" r:id="rId3" display="info@sengli.com.my"/>
+    <hyperlink ref="H2" r:id="rId4" display="https://www.sengli.com.my/mobile/home"/>
+    <hyperlink ref="H3" r:id="rId4" display="https://www.sengli.com.my/mobile/home"/>
+    <hyperlink ref="H4" r:id="rId4" display="https://www.sengli.com.my/mobile/home"/>
+    <hyperlink ref="F5" r:id="rId5" display="man858100@gmail.com" tooltip="mailto:man858100@gmail.com"/>
+    <hyperlink ref="H5" r:id="rId4" display="https://www.sengli.com.my/mobile/home"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/staff.xlsx
+++ b/staff.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9708"/>
+    <workbookView windowWidth="23040" windowHeight="9768"/>
   </bookViews>
   <sheets>
     <sheet name="staff" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
   <si>
     <t>id</t>
   </si>
@@ -120,6 +120,21 @@
   </si>
   <si>
     <t>images/man.png</t>
+  </si>
+  <si>
+    <t>shawn</t>
+  </si>
+  <si>
+    <t>Shawn Lee</t>
+  </si>
+  <si>
+    <t>CIO</t>
+  </si>
+  <si>
+    <t>shawnlee@sengli.com.my</t>
+  </si>
+  <si>
+    <t>images/shawn.png</t>
   </si>
 </sst>
 </file>
@@ -132,7 +147,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,6 +159,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -608,138 +631,141 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1275,8 +1301,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelRow="4"/>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelRow="5"/>
   <cols>
     <col min="5" max="5" width="12.8888888888889"/>
     <col min="6" max="6" width="54.2222222222222" customWidth="1"/>
@@ -1428,16 +1454,47 @@
         <v>30</v>
       </c>
     </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>60167738581</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6">
+        <v>60167738581</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" display="qianhuistudyarea@gmail.com"/>
-    <hyperlink ref="F3" r:id="rId2" display="jaredlow@sengli.com.my"/>
+    <hyperlink ref="F3" r:id="rId2" display="jaredlow@sengli.com.my" tooltip="mailto:jaredlow@sengli.com.my"/>
     <hyperlink ref="F4" r:id="rId3" display="info@sengli.com.my"/>
     <hyperlink ref="H2" r:id="rId4" display="https://www.sengli.com.my/mobile/home"/>
     <hyperlink ref="H3" r:id="rId4" display="https://www.sengli.com.my/mobile/home"/>
     <hyperlink ref="H4" r:id="rId4" display="https://www.sengli.com.my/mobile/home"/>
     <hyperlink ref="F5" r:id="rId5" display="man858100@gmail.com" tooltip="mailto:man858100@gmail.com"/>
     <hyperlink ref="H5" r:id="rId4" display="https://www.sengli.com.my/mobile/home"/>
+    <hyperlink ref="H6" r:id="rId4" display="https://www.sengli.com.my/mobile/home"/>
+    <hyperlink ref="F6" r:id="rId6" display="shawnlee@sengli.com.my" tooltip="mailto:shawnlee@sengli.com.my"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/staff.xlsx
+++ b/staff.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9768"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="staff" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
     <t>qianhui</t>
   </si>
   <si>
-    <t>Qian Hui Liong</t>
+    <t>Liong Qian Hui Nicolle</t>
   </si>
   <si>
     <t>Data</t>
@@ -80,7 +80,7 @@
     <t>jared</t>
   </si>
   <si>
-    <t>Jared Low</t>
+    <t>Jared Low Liang Shen</t>
   </si>
   <si>
     <t>CFO</t>
@@ -95,7 +95,7 @@
     <t>kelly</t>
   </si>
   <si>
-    <t>Kelly Chan</t>
+    <t>Kelly Chan Khe Lee</t>
   </si>
   <si>
     <t>Account (AP)</t>
@@ -125,10 +125,10 @@
     <t>shawn</t>
   </si>
   <si>
-    <t>Shawn Lee</t>
-  </si>
-  <si>
-    <t>CIO</t>
+    <t>Lee Ah Seng (Shawn)</t>
+  </si>
+  <si>
+    <t>Director</t>
   </si>
   <si>
     <t>shawnlee@sengli.com.my</t>
@@ -613,159 +613,160 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1304,9 +1305,10 @@
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelRow="5"/>
   <cols>
-    <col min="5" max="5" width="12.8888888888889"/>
-    <col min="6" max="6" width="54.2222222222222" customWidth="1"/>
-    <col min="7" max="7" width="12.8888888888889"/>
+    <col min="2" max="2" width="19.3333333333333" customWidth="1"/>
+    <col min="5" max="5" width="12.8888888888889" style="1" customWidth="1"/>
+    <col min="6" max="6" width="54.2222222222222" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.8888888888889" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1354,13 +1356,13 @@
       <c r="E2">
         <v>60143986456</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G2">
         <v>60143986456</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I2" t="s">
@@ -1383,13 +1385,13 @@
       <c r="E3">
         <v>60107608581</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G3">
         <v>60107608581</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I3" t="s">
@@ -1412,13 +1414,13 @@
       <c r="E4">
         <v>60167388581</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G4">
         <v>60167388581</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I4" t="s">
@@ -1441,13 +1443,13 @@
       <c r="E5">
         <v>60129228661</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G5">
         <v>60129228661</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I5" t="s">
@@ -1470,13 +1472,13 @@
       <c r="E6">
         <v>60167738581</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G6">
         <v>60167738581</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I6" t="s">
@@ -1486,15 +1488,15 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" display="qianhuistudyarea@gmail.com"/>
-    <hyperlink ref="F3" r:id="rId2" display="jaredlow@sengli.com.my" tooltip="mailto:jaredlow@sengli.com.my"/>
-    <hyperlink ref="F4" r:id="rId3" display="info@sengli.com.my"/>
-    <hyperlink ref="H2" r:id="rId4" display="https://www.sengli.com.my/mobile/home"/>
-    <hyperlink ref="H3" r:id="rId4" display="https://www.sengli.com.my/mobile/home"/>
-    <hyperlink ref="H4" r:id="rId4" display="https://www.sengli.com.my/mobile/home"/>
+    <hyperlink ref="H2" r:id="rId2" display="https://www.sengli.com.my/mobile/home"/>
+    <hyperlink ref="F3" r:id="rId3" display="jaredlow@sengli.com.my" tooltip="mailto:jaredlow@sengli.com.my"/>
+    <hyperlink ref="H3" r:id="rId2" display="https://www.sengli.com.my/mobile/home"/>
+    <hyperlink ref="F4" r:id="rId4" display="info@sengli.com.my"/>
+    <hyperlink ref="H4" r:id="rId2" display="https://www.sengli.com.my/mobile/home"/>
     <hyperlink ref="F5" r:id="rId5" display="man858100@gmail.com" tooltip="mailto:man858100@gmail.com"/>
-    <hyperlink ref="H5" r:id="rId4" display="https://www.sengli.com.my/mobile/home"/>
-    <hyperlink ref="H6" r:id="rId4" display="https://www.sengli.com.my/mobile/home"/>
+    <hyperlink ref="H5" r:id="rId2" display="https://www.sengli.com.my/mobile/home"/>
     <hyperlink ref="F6" r:id="rId6" display="shawnlee@sengli.com.my" tooltip="mailto:shawnlee@sengli.com.my"/>
+    <hyperlink ref="H6" r:id="rId2" display="https://www.sengli.com.my/mobile/home"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/staff.xlsx
+++ b/staff.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="11520" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="staff" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="41">
   <si>
     <t>id</t>
   </si>
@@ -62,7 +62,7 @@
     <t>Liong Qian Hui Nicolle</t>
   </si>
   <si>
-    <t>Data</t>
+    <t>Data and Business Analyst</t>
   </si>
   <si>
     <t>SENG LI MARKETING SDN BHD</t>
@@ -83,7 +83,7 @@
     <t>Jared Low Liang Shen</t>
   </si>
   <si>
-    <t>CFO</t>
+    <t>Chief Financial Officer</t>
   </si>
   <si>
     <t>jaredlow@sengli.com.my</t>
@@ -92,21 +92,6 @@
     <t>images/jared.png</t>
   </si>
   <si>
-    <t>kelly</t>
-  </si>
-  <si>
-    <t>Kelly Chan Khe Lee</t>
-  </si>
-  <si>
-    <t>Account (AP)</t>
-  </si>
-  <si>
-    <t>info@sengli.com.my</t>
-  </si>
-  <si>
-    <t>images/kelly.png</t>
-  </si>
-  <si>
     <t>man</t>
   </si>
   <si>
@@ -135,6 +120,36 @@
   </si>
   <si>
     <t>images/shawn.png</t>
+  </si>
+  <si>
+    <t>stephent</t>
+  </si>
+  <si>
+    <t>Stephent Lee</t>
+  </si>
+  <si>
+    <t>Chief Executive Officer</t>
+  </si>
+  <si>
+    <t>stephent8581@gmail.com</t>
+  </si>
+  <si>
+    <t>images/stephent.png</t>
+  </si>
+  <si>
+    <t>lee</t>
+  </si>
+  <si>
+    <t>Lee Aik Li (Lee)</t>
+  </si>
+  <si>
+    <t>Chief Operating Officer</t>
+  </si>
+  <si>
+    <t>lee@sengli.com.my</t>
+  </si>
+  <si>
+    <t>images/lee.png</t>
   </si>
 </sst>
 </file>
@@ -758,7 +773,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -767,6 +782,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1302,10 +1320,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelRow="6"/>
   <cols>
     <col min="2" max="2" width="19.3333333333333" customWidth="1"/>
+    <col min="4" max="4" width="23.5555555555556" customWidth="1"/>
     <col min="5" max="5" width="12.8888888888889" style="1" customWidth="1"/>
     <col min="6" max="6" width="54.2222222222222" style="1" customWidth="1"/>
     <col min="7" max="7" width="12.8888888888889" style="1" customWidth="1"/>
@@ -1412,13 +1431,13 @@
         <v>12</v>
       </c>
       <c r="E4">
-        <v>60167388581</v>
+        <v>60129228661</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G4">
-        <v>60167388581</v>
+        <v>60129228661</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>14</v>
@@ -1441,13 +1460,13 @@
         <v>12</v>
       </c>
       <c r="E5">
-        <v>60129228661</v>
-      </c>
-      <c r="F5" s="2" t="s">
+        <v>60167738581</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>29</v>
       </c>
       <c r="G5">
-        <v>60129228661</v>
+        <v>60167738581</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>14</v>
@@ -1469,20 +1488,49 @@
       <c r="D6" t="s">
         <v>12</v>
       </c>
-      <c r="E6">
-        <v>60167738581</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="E6" s="1">
+        <v>60167008581</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G6">
-        <v>60167738581</v>
+      <c r="G6" s="1">
+        <v>60167008581</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I6" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="1">
+        <v>60137698581</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="1">
+        <v>60137698581</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1491,12 +1539,14 @@
     <hyperlink ref="H2" r:id="rId2" display="https://www.sengli.com.my/mobile/home"/>
     <hyperlink ref="F3" r:id="rId3" display="jaredlow@sengli.com.my" tooltip="mailto:jaredlow@sengli.com.my"/>
     <hyperlink ref="H3" r:id="rId2" display="https://www.sengli.com.my/mobile/home"/>
-    <hyperlink ref="F4" r:id="rId4" display="info@sengli.com.my"/>
+    <hyperlink ref="F4" r:id="rId4" display="man858100@gmail.com" tooltip="mailto:man858100@gmail.com"/>
     <hyperlink ref="H4" r:id="rId2" display="https://www.sengli.com.my/mobile/home"/>
-    <hyperlink ref="F5" r:id="rId5" display="man858100@gmail.com" tooltip="mailto:man858100@gmail.com"/>
+    <hyperlink ref="F5" r:id="rId5" display="shawnlee@sengli.com.my" tooltip="mailto:shawnlee@sengli.com.my"/>
     <hyperlink ref="H5" r:id="rId2" display="https://www.sengli.com.my/mobile/home"/>
-    <hyperlink ref="F6" r:id="rId6" display="shawnlee@sengli.com.my" tooltip="mailto:shawnlee@sengli.com.my"/>
+    <hyperlink ref="F6" r:id="rId6" display="stephent8581@gmail.com" tooltip="mailto:stephent8581@gmail.com"/>
+    <hyperlink ref="H7" r:id="rId2" display="https://www.sengli.com.my/mobile/home"/>
     <hyperlink ref="H6" r:id="rId2" display="https://www.sengli.com.my/mobile/home"/>
+    <hyperlink ref="F7" r:id="rId7" display="lee@sengli.com.my"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
